--- a/TestData/T1592_ValidationsToBeCompleted.xlsx
+++ b/TestData/T1592_ValidationsToBeCompleted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19AB1C2-DC42-4507-9AE8-092E4A4CBD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BBA67C6-0D87-4D45-8515-E85230D42586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="2385" windowWidth="21420" windowHeight="10275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -54,9 +54,6 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -355,6 +352,9 @@
   </si>
   <si>
     <t>Error:, Estimated Financials - EBITDA(MM) is required.</t>
+  </si>
+  <si>
+    <t>CSDN-0000001546</t>
   </si>
 </sst>
 </file>
@@ -757,153 +757,153 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
+        <v>98</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="U2" t="s">
+        <v>30</v>
+      </c>
+      <c r="V2" t="s">
         <v>99</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q2" s="3" t="s">
+      <c r="W2" t="s">
+        <v>33</v>
+      </c>
+      <c r="X2" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="R2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" t="s">
-        <v>28</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" t="s">
-        <v>100</v>
-      </c>
-      <c r="W2" t="s">
-        <v>34</v>
-      </c>
-      <c r="X2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA2" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="AB2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -923,18 +923,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -960,80 +960,80 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="C1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="H1" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>96</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="162" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>0</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="J3" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1073,198 +1073,198 @@
   <sheetData>
     <row r="1" spans="1:32" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>60</v>
-      </c>
       <c r="D1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="P1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="Q1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="9" t="s">
-        <v>75</v>
       </c>
       <c r="S1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="T1" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="V1" s="9" t="s">
+      <c r="W1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="X1" s="9" t="s">
+      <c r="Y1" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Z1" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" s="9" t="s">
-        <v>84</v>
-      </c>
       <c r="AA1" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="AB1" s="9" t="s">
+      <c r="AC1" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AC1" s="9" t="s">
+      <c r="AD1" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="AD1" s="9" t="s">
+      <c r="AE1" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="AE1" s="9" t="s">
+      <c r="AF1" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="AF1" s="9" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="T2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="U2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="V2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="X2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF2" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="S2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="Z2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AB2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.25">
